--- a/outputs/5835.xlsx
+++ b/outputs/5835.xlsx
@@ -41,9 +41,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -140,7 +141,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
@@ -159,15 +163,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -175,27 +183,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -455,47 +459,46 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.84"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>2012</v>
       </c>
-      <c r="C3" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B3)*($H$3:$H$18=$A3)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B3)*($H$3:$H$18=$A3),0),0)))</f>
+      <c r="C3" s="3" t="n">
         <v>4.2694004291186</v>
       </c>
       <c r="G3" s="11" t="n">
@@ -508,15 +511,14 @@
         <v>4.2694004291186</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>2011</v>
       </c>
-      <c r="C4" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B4)*($H$3:$H$18=$A4)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B4)*($H$3:$H$18=$A4),0),0)))</f>
+      <c r="C4" s="3" t="n">
         <v>5.44723924245699</v>
       </c>
       <c r="G4" s="11" t="n">
@@ -529,15 +531,14 @@
         <v>5.44723924245699</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="C5" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B5)*($H$3:$H$18=$A5)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B5)*($H$3:$H$18=$A5),0),0)))</f>
+      <c r="C5" s="3" t="n">
         <v>5.12251642820236</v>
       </c>
       <c r="G5" s="11" t="n">
@@ -550,17 +551,14 @@
         <v>5.12251642820236</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>2009</v>
       </c>
-      <c r="C6" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B6)*($H$3:$H$18=$A6)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B6)*($H$3:$H$18=$A6),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C6" s="3"/>
       <c r="G6" s="11" t="n">
         <v>2009</v>
       </c>
@@ -569,16 +567,15 @@
       </c>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>2008</v>
       </c>
-      <c r="C7" s="3" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B7)*($H$3:$H$18=$A7)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B7)*($H$3:$H$18=$A7),0),0)))</f>
-        <v/>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>2014</v>
@@ -588,16 +585,15 @@
       </c>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>2007</v>
       </c>
-      <c r="C8" s="3" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B8)*($H$3:$H$18=$A8)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B8)*($H$3:$H$18=$A8),0),0)))</f>
-        <v/>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>2013</v>
@@ -607,16 +603,15 @@
       </c>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>2006</v>
       </c>
-      <c r="C9" s="3" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B9)*($H$3:$H$18=$A9)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B9)*($H$3:$H$18=$A9),0),0)))</f>
-        <v/>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>2012</v>
@@ -626,17 +621,14 @@
       </c>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>2005</v>
       </c>
-      <c r="C10" s="3" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B10)*($H$3:$H$18=$A10)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B10)*($H$3:$H$18=$A10),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C10" s="3"/>
       <c r="G10" s="11" t="n">
         <v>2011</v>
       </c>
@@ -647,17 +639,14 @@
         <v>3.73675856522542</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
         <v>102012</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>2004</v>
       </c>
-      <c r="C11" s="3" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B11)*($H$3:$H$18=$A11)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B11)*($H$3:$H$18=$A11),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C11" s="3"/>
       <c r="G11" s="11" t="n">
         <v>2010</v>
       </c>
@@ -668,17 +657,14 @@
         <v>4.74940530511316</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>2014</v>
       </c>
-      <c r="C12" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B12)*($H$3:$H$18=$A12)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B12)*($H$3:$H$18=$A12),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C12" s="3"/>
       <c r="G12" s="11" t="n">
         <v>2009</v>
       </c>
@@ -687,17 +673,14 @@
       </c>
       <c r="I12" s="12"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>2013</v>
       </c>
-      <c r="C13" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B13)*($H$3:$H$18=$A13)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B13)*($H$3:$H$18=$A13),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C13" s="3"/>
       <c r="G13" s="11" t="n">
         <v>2008</v>
       </c>
@@ -708,17 +691,14 @@
         <v>4.23426987963461</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>2012</v>
       </c>
-      <c r="C14" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B14)*($H$3:$H$18=$A14)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B14)*($H$3:$H$18=$A14),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C14" s="3"/>
       <c r="G14" s="11" t="n">
         <v>2007</v>
       </c>
@@ -729,15 +709,14 @@
         <v>3.53263858256949</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>2011</v>
       </c>
-      <c r="C15" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B15)*($H$3:$H$18=$A15)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B15)*($H$3:$H$18=$A15),0),0)))</f>
+      <c r="C15" s="3" t="n">
         <v>3.73675856522542</v>
       </c>
       <c r="G15" s="11" t="n">
@@ -750,15 +729,14 @@
         <v>3.84974597515049</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="C16" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B16)*($H$3:$H$18=$A16)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B16)*($H$3:$H$18=$A16),0),0)))</f>
+      <c r="C16" s="3" t="n">
         <v>4.74940530511316</v>
       </c>
       <c r="G16" s="11" t="n">
@@ -771,17 +749,14 @@
         <v>3.73902904676592</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>2009</v>
       </c>
-      <c r="C17" s="10" t="str">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B17)*($H$3:$H$18=$A17)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B17)*($H$3:$H$18=$A17),0),0)))</f>
-        <v/>
-      </c>
+      <c r="C17" s="3"/>
       <c r="G17" s="11" t="n">
         <v>2010</v>
       </c>
@@ -792,15 +767,14 @@
         <v>3.97432324684873</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>2008</v>
       </c>
-      <c r="C18" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B18)*($H$3:$H$18=$A18)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B18)*($H$3:$H$18=$A18),0),0)))</f>
+      <c r="C18" s="3" t="n">
         <v>4.23426987963461</v>
       </c>
       <c r="G18" s="11" t="n">
@@ -813,15 +787,14 @@
         <v>6.43538379836063</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>103010</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>2007</v>
       </c>
-      <c r="C19" s="10" t="n">
-        <f aca="false">IF(SUMPRODUCT(($G$3:$G$18=$B19)*($H$3:$H$18=$A19)*($I$3:$I$18&lt;&gt;""))=0,"",INDEX($I$3:$I$18,MATCH(1,INDEX(($G$3:$G$18=$B19)*($H$3:$H$18=$A19),0),0)))</f>
+      <c r="C19" s="3" t="n">
         <v>3.53263858256949</v>
       </c>
     </row>
